--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00155_18880712/oocihm.N_00155_18880712.2.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00155_18880712/oocihm.N_00155_18880712.2.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -1019,7 +1019,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00155_18880712/oocihm.N_00155_18880712.2.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00155_18880712/oocihm.N_00155_18880712.2.xlsx
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y60"/>
+  <dimension ref="A1:Y18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.N_00155_18880712\oocihm.N_00155_18880712.2.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.N_00155_18880712\oocihm.N_00155_18880712.2.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00155_18880712\oocihm.N_00155_18880712.2.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00155_18880712\oocihm.N_00155_18880712.2.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
@@ -617,16 +617,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L9: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Drowned-Excitement at Niagara â€”</t>
+          <t>L877: stray/suspicious non-ASCII glyph(s): U+FF1B FULLWIDTH SEMICOLON :: acclamation； Birtle, C. J. Mickle, Liberal,</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L7: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: THE "TIMESâ€™ " THUNDER.</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]/</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]/</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L132: isolated marker/symbol line :: "</t>
@@ -634,7 +638,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L5: isolated marker/symbol line :: 2</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]/</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -650,7 +654,7 @@
       <c r="R2" s="1" t="inlineStr"/>
       <c r="S2" s="1" t="inlineStr">
         <is>
-          <t>L103: line starts with digit/letter garbage token | suspicious token(s): 3Yesterday (letter/digit mix) :: 3Yesterday Attorney-General Webster</t>
+          <t>L11: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Clear Statement of the Differences</t>
         </is>
       </c>
       <c r="T2" s="1" t="inlineStr">
@@ -689,7 +693,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>1122</t>
+          <t>972</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -712,12 +716,12 @@
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L441: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): LoNDoN (odd internal casing) :: LoNDoN, Ont., July 6.â€” A conference of</t>
+          <t>L1068: stray/suspicious non-ASCII glyph(s): U+4EE5 CJK UNIFIED IDEOGRAPH-4EE5 :: 1 以</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L11: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ Clear Statement of the Differences</t>
+          <t>L11: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Clear Statement of the Differences</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -729,7 +733,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L418: isolated marker/symbol line :: %</t>
+          <t>L5: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr">
@@ -745,7 +749,7 @@
       <c r="R3" s="1" t="inlineStr"/>
       <c r="S3" s="1" t="inlineStr">
         <is>
-          <t>L111: line starts with punctuation glued to text :: * Mr. Parnell is here. I have spoken to</t>
+          <t>L103: line starts with digit/letter garbage token | suspicious token(s): 3Yesterday (letter/digit mix) :: 3Yesterday Attorney-General Webster</t>
         </is>
       </c>
       <c r="T3" s="1" t="inlineStr"/>
@@ -780,7 +784,7 @@
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>7020</t>
+          <t>7019</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr"/>
@@ -793,7 +797,7 @@
       <c r="G4" s="1" t="inlineStr"/>
       <c r="H4" s="1" t="inlineStr">
         <is>
-          <t>L441: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): LoNDoN (odd internal casing) :: LoNDoN, Ont., July 6.â€” A conference of</t>
+          <t>L441: suspicious token(s): LoNDoN (odd internal casing) :: LoNDoN, Ont., July 6.— A conference of</t>
         </is>
       </c>
       <c r="I4" s="1" t="inlineStr">
@@ -803,12 +807,12 @@
       </c>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L1068: stray/suspicious non-ASCII glyph(s): U+00A5 YEN SIGN :: 1 ä»¥</t>
+          <t>L1110: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L84: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Careyâ€™s Grave.</t>
+          <t>L198: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: ness-shire.•</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -820,7 +824,7 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L1021: symbol-only separator/garbage line :: $1,200,000.________. _________</t>
+          <t>L418: isolated marker/symbol line :: %</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr">
@@ -836,7 +840,7 @@
       <c r="R4" s="1" t="inlineStr"/>
       <c r="S4" s="1" t="inlineStr">
         <is>
-          <t>L227: line starts with digit/letter garbage token | suspicious token(s): 1TheNorthBritish (letter/digit mix) :: 1TheNorthBritish Railway Company</t>
+          <t>L111: line starts with punctuation glued to text :: * Mr. Parnell is here. I have spoken to</t>
         </is>
       </c>
       <c r="T4" s="1" t="inlineStr"/>
@@ -867,7 +871,7 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -888,14 +892,10 @@
           <t>L338: suspicious token(s): There2 (letter/digit mix) :: your giving the amount asked for. There2</t>
         </is>
       </c>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>L1110: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
-        </is>
-      </c>
+      <c r="J5" s="1" t="inlineStr"/>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L163: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: will be remembered that the coronerâ€™s in-</t>
+          <t>L313: stray/suspicious non-ASCII glyph(s): U+25A0 BLACK SQUARE :: SET OF GRAVE CHARGES.■</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
@@ -907,7 +907,7 @@
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L1122: isolated marker/symbol line :: /</t>
+          <t>L1021: symbol-only separator/garbage line :: $1,200,000.________. _________</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr">
@@ -923,7 +923,7 @@
       <c r="R5" s="1" t="inlineStr"/>
       <c r="S5" s="1" t="inlineStr">
         <is>
-          <t>L945: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | line starts with digit/letter garbage token | suspicious token(s): 1self (letter/digit mix) :: 1self from the fastenings and failed. His | cost $6,000. At 3 oâ€™clock Mr. P. J. Cook,</t>
+          <t>L227: line starts with digit/letter garbage token | suspicious token(s): 1TheNorthBritish (letter/digit mix) :: 1TheNorthBritish Railway Company</t>
         </is>
       </c>
       <c r="T5" s="1" t="inlineStr"/>
@@ -968,13 +968,13 @@
       </c>
       <c r="I6" s="1" t="inlineStr">
         <is>
-          <t>L466: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): 10It (letter/digit mix) :: 10It does not seem so probable that Oâ€™Don-</t>
+          <t>L466: suspicious token(s): 10It (letter/digit mix) :: 10It does not seem so probable that O’Don-</t>
         </is>
       </c>
       <c r="J6" s="1" t="inlineStr"/>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>L168: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: the town mourned over the informerâ€™s fate.</t>
+          <t>L970: stray/suspicious non-ASCII glyph(s): U+25A0 BLACK SQUARE :: ■hem from any more attempts of a like the truth that made good citizens and good</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr"/>
@@ -984,7 +984,11 @@
           <t>L286: isolated marker/symbol line :: 0</t>
         </is>
       </c>
-      <c r="O6" s="1" t="inlineStr"/>
+      <c r="O6" s="1" t="inlineStr">
+        <is>
+          <t>L1122: isolated marker/symbol line :: /</t>
+        </is>
+      </c>
       <c r="P6" s="1" t="inlineStr">
         <is>
           <t>L1049: punctuation artifact: repeated periods :: of the particularity with which the Times...</t>
@@ -998,7 +1002,7 @@
       <c r="R6" s="1" t="inlineStr"/>
       <c r="S6" s="1" t="inlineStr">
         <is>
-          <t>L965: line starts with digit/letter garbage token | suspicious token(s): 1victim (letter/digit mix) :: 1victim to the list of those foolhardy, life- upon the power of Christian forces and the</t>
+          <t>L945: line starts with digit/letter garbage token | suspicious token(s): 1self (letter/digit mix) :: 1self from the fastenings and failed. His | cost $6,000. At 3 o’clock Mr. P. J. Cook,</t>
         </is>
       </c>
       <c r="T6" s="1" t="inlineStr"/>
@@ -1049,7 +1053,7 @@
       <c r="J7" s="1" t="inlineStr"/>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>L198: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: ness-shire.â€¢</t>
+          <t>L1111: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: double/multiple hyphen; hyphen/bullet debris :: stream, where Flack was continually -----------•-------------</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr"/>
@@ -1067,7 +1071,11 @@
         </is>
       </c>
       <c r="R7" s="1" t="inlineStr"/>
-      <c r="S7" s="1" t="inlineStr"/>
+      <c r="S7" s="1" t="inlineStr">
+        <is>
+          <t>L965: line starts with digit/letter garbage token | suspicious token(s): 1victim (letter/digit mix) :: 1victim to the list of those foolhardy, life- upon the power of Christian forces and the</t>
+        </is>
+      </c>
       <c r="T7" s="1" t="inlineStr"/>
       <c r="U7" s="1" t="inlineStr"/>
       <c r="V7" s="1" t="inlineStr">
@@ -1110,11 +1118,7 @@
         </is>
       </c>
       <c r="J8" s="1" t="inlineStr"/>
-      <c r="K8" s="1" t="inlineStr">
-        <is>
-          <t>L247: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: LONDON, July 4.â€”The Pan-Presbyterian</t>
-        </is>
-      </c>
+      <c r="K8" s="1" t="inlineStr"/>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
@@ -1126,7 +1130,7 @@
       <c r="P8" s="1" t="inlineStr"/>
       <c r="Q8" s="1" t="inlineStr">
         <is>
-          <t>L1111: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: double/multiple hyphen :: stream, where Flack was continually -----------â€¢-------------</t>
+          <t>L1111: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: double/multiple hyphen; hyphen/bullet debris :: stream, where Flack was continually -----------•-------------</t>
         </is>
       </c>
       <c r="R8" s="1" t="inlineStr"/>
@@ -1169,15 +1173,11 @@
       </c>
       <c r="I9" s="1" t="inlineStr">
         <is>
-          <t>L945: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | line starts with digit/letter garbage token | suspicious token(s): 1self (letter/digit mix) :: 1self from the fastenings and failed. His | cost $6,000. At 3 oâ€™clock Mr. P. J. Cook,</t>
+          <t>L945: line starts with digit/letter garbage token | suspicious token(s): 1self (letter/digit mix) :: 1self from the fastenings and failed. His | cost $6,000. At 3 o’clock Mr. P. J. Cook,</t>
         </is>
       </c>
       <c r="J9" s="1" t="inlineStr"/>
-      <c r="K9" s="1" t="inlineStr">
-        <is>
-          <t>L271: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: A last (Thursday) nightâ€™s London cable</t>
-        </is>
-      </c>
+      <c r="K9" s="1" t="inlineStr"/>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
@@ -1205,12 +1205,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1224,11 +1224,7 @@
         </is>
       </c>
       <c r="J10" s="1" t="inlineStr"/>
-      <c r="K10" s="1" t="inlineStr">
-        <is>
-          <t>L310: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Foolish Flackâ€™s Fatal Voyage in the</t>
-        </is>
-      </c>
+      <c r="K10" s="1" t="inlineStr"/>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
@@ -1261,7 +1257,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1271,11 +1267,7 @@
       <c r="H11" s="1" t="inlineStr"/>
       <c r="I11" s="1" t="inlineStr"/>
       <c r="J11" s="1" t="inlineStr"/>
-      <c r="K11" s="1" t="inlineStr">
-        <is>
-          <t>L325: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: with the Oâ€™Donnell-Times trial. He said</t>
-        </is>
-      </c>
+      <c r="K11" s="1" t="inlineStr"/>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
@@ -1308,7 +1300,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1318,11 +1310,7 @@
       <c r="H12" s="1" t="inlineStr"/>
       <c r="I12" s="1" t="inlineStr"/>
       <c r="J12" s="1" t="inlineStr"/>
-      <c r="K12" s="1" t="inlineStr">
-        <is>
-          <t>L329: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: clared that he never saw Patrick Eganâ€™s</t>
-        </is>
-      </c>
+      <c r="K12" s="1" t="inlineStr"/>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
@@ -1365,11 +1353,7 @@
       <c r="H13" s="1" t="inlineStr"/>
       <c r="I13" s="1" t="inlineStr"/>
       <c r="J13" s="1" t="inlineStr"/>
-      <c r="K13" s="1" t="inlineStr">
-        <is>
-          <t>L342: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: lect it. As to Eganâ€™s letter of October</t>
-        </is>
-      </c>
+      <c r="K13" s="1" t="inlineStr"/>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
@@ -1402,7 +1386,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1412,11 +1396,7 @@
       <c r="H14" s="1" t="inlineStr"/>
       <c r="I14" s="1" t="inlineStr"/>
       <c r="J14" s="1" t="inlineStr"/>
-      <c r="K14" s="1" t="inlineStr">
-        <is>
-          <t>L347: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: in Careyâ€™s house, Mr. Parnell said that</t>
-        </is>
-      </c>
+      <c r="K14" s="1" t="inlineStr"/>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
@@ -1459,11 +1439,7 @@
       <c r="H15" s="1" t="inlineStr"/>
       <c r="I15" s="1" t="inlineStr"/>
       <c r="J15" s="1" t="inlineStr"/>
-      <c r="K15" s="1" t="inlineStr">
-        <is>
-          <t>L430: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: omical expenditures and a lowered tariff.â€”</t>
-        </is>
-      </c>
+      <c r="K15" s="1" t="inlineStr"/>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
@@ -1506,11 +1482,7 @@
       <c r="H16" s="1" t="inlineStr"/>
       <c r="I16" s="1" t="inlineStr"/>
       <c r="J16" s="1" t="inlineStr"/>
-      <c r="K16" s="1" t="inlineStr">
-        <is>
-          <t>L444: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: â€˜* The great majority of the letters read at</t>
-        </is>
-      </c>
+      <c r="K16" s="1" t="inlineStr"/>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr">
@@ -1553,11 +1525,7 @@
       <c r="H17" s="1" t="inlineStr"/>
       <c r="I17" s="1" t="inlineStr"/>
       <c r="J17" s="1" t="inlineStr"/>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>L466: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): 10It (letter/digit mix) :: 10It does not seem so probable that Oâ€™Don-</t>
-        </is>
-      </c>
+      <c r="K17" s="1" t="inlineStr"/>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
@@ -1588,16 +1556,12 @@
       <c r="H18" s="1" t="inlineStr"/>
       <c r="I18" s="1" t="inlineStr"/>
       <c r="J18" s="1" t="inlineStr"/>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t>L512: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: left the hotel at 2.15 oâ€™clock and walked |</t>
-        </is>
-      </c>
+      <c r="K18" s="1" t="inlineStr"/>
       <c r="L18" s="1" t="inlineStr"/>
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>L1110: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L1110: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr"/>
@@ -1612,1308 +1576,6 @@
       <c r="X18" s="1" t="inlineStr"/>
       <c r="Y18" s="1" t="inlineStr"/>
     </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr"/>
-      <c r="B19" s="1" t="inlineStr"/>
-      <c r="C19" s="1" t="inlineStr"/>
-      <c r="D19" s="1" t="inlineStr"/>
-      <c r="E19" s="1" t="inlineStr"/>
-      <c r="F19" s="1" t="inlineStr"/>
-      <c r="G19" s="1" t="inlineStr"/>
-      <c r="H19" s="1" t="inlineStr"/>
-      <c r="I19" s="1" t="inlineStr"/>
-      <c r="J19" s="1" t="inlineStr"/>
-      <c r="K19" s="1" t="inlineStr">
-        <is>
-          <t>L569: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: the entrance to Gordonâ€™s College, Aber-</t>
-        </is>
-      </c>
-      <c r="L19" s="1" t="inlineStr"/>
-      <c r="M19" s="1" t="inlineStr"/>
-      <c r="N19" s="1" t="inlineStr"/>
-      <c r="O19" s="1" t="inlineStr"/>
-      <c r="P19" s="1" t="inlineStr"/>
-      <c r="Q19" s="1" t="inlineStr"/>
-      <c r="R19" s="1" t="inlineStr"/>
-      <c r="S19" s="1" t="inlineStr"/>
-      <c r="T19" s="1" t="inlineStr"/>
-      <c r="U19" s="1" t="inlineStr"/>
-      <c r="V19" s="1" t="inlineStr"/>
-      <c r="W19" s="1" t="inlineStr"/>
-      <c r="X19" s="1" t="inlineStr"/>
-      <c r="Y19" s="1" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr"/>
-      <c r="B20" s="1" t="inlineStr"/>
-      <c r="C20" s="1" t="inlineStr"/>
-      <c r="D20" s="1" t="inlineStr"/>
-      <c r="E20" s="1" t="inlineStr"/>
-      <c r="F20" s="1" t="inlineStr"/>
-      <c r="G20" s="1" t="inlineStr"/>
-      <c r="H20" s="1" t="inlineStr"/>
-      <c r="I20" s="1" t="inlineStr"/>
-      <c r="J20" s="1" t="inlineStr"/>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
-          <t>L585: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: beadle the waur oâ€™ a dram one day, threat-</t>
-        </is>
-      </c>
-      <c r="L20" s="1" t="inlineStr"/>
-      <c r="M20" s="1" t="inlineStr"/>
-      <c r="N20" s="1" t="inlineStr"/>
-      <c r="O20" s="1" t="inlineStr"/>
-      <c r="P20" s="1" t="inlineStr"/>
-      <c r="Q20" s="1" t="inlineStr"/>
-      <c r="R20" s="1" t="inlineStr"/>
-      <c r="S20" s="1" t="inlineStr"/>
-      <c r="T20" s="1" t="inlineStr"/>
-      <c r="U20" s="1" t="inlineStr"/>
-      <c r="V20" s="1" t="inlineStr"/>
-      <c r="W20" s="1" t="inlineStr"/>
-      <c r="X20" s="1" t="inlineStr"/>
-      <c r="Y20" s="1" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr"/>
-      <c r="B21" s="1" t="inlineStr"/>
-      <c r="C21" s="1" t="inlineStr"/>
-      <c r="D21" s="1" t="inlineStr"/>
-      <c r="E21" s="1" t="inlineStr"/>
-      <c r="F21" s="1" t="inlineStr"/>
-      <c r="G21" s="1" t="inlineStr"/>
-      <c r="H21" s="1" t="inlineStr"/>
-      <c r="I21" s="1" t="inlineStr"/>
-      <c r="J21" s="1" t="inlineStr"/>
-      <c r="K21" s="1" t="inlineStr">
-        <is>
-          <t>L588: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE, U+2122 TRADE MARK SIGN :: â€˜I hae happit mony a fauâ€™t oâ€™ yours, anâ€™ I</t>
-        </is>
-      </c>
-      <c r="L21" s="1" t="inlineStr"/>
-      <c r="M21" s="1" t="inlineStr"/>
-      <c r="N21" s="1" t="inlineStr"/>
-      <c r="O21" s="1" t="inlineStr"/>
-      <c r="P21" s="1" t="inlineStr"/>
-      <c r="Q21" s="1" t="inlineStr"/>
-      <c r="R21" s="1" t="inlineStr"/>
-      <c r="S21" s="1" t="inlineStr"/>
-      <c r="T21" s="1" t="inlineStr"/>
-      <c r="U21" s="1" t="inlineStr"/>
-      <c r="V21" s="1" t="inlineStr"/>
-      <c r="W21" s="1" t="inlineStr"/>
-      <c r="X21" s="1" t="inlineStr"/>
-      <c r="Y21" s="1" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr"/>
-      <c r="B22" s="1" t="inlineStr"/>
-      <c r="C22" s="1" t="inlineStr"/>
-      <c r="D22" s="1" t="inlineStr"/>
-      <c r="E22" s="1" t="inlineStr"/>
-      <c r="F22" s="1" t="inlineStr"/>
-      <c r="G22" s="1" t="inlineStr"/>
-      <c r="H22" s="1" t="inlineStr"/>
-      <c r="I22" s="1" t="inlineStr"/>
-      <c r="J22" s="1" t="inlineStr"/>
-      <c r="K22" s="1" t="inlineStr">
-        <is>
-          <t>L589: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: think ye micht thole ane oâ€™ mine."</t>
-        </is>
-      </c>
-      <c r="L22" s="1" t="inlineStr"/>
-      <c r="M22" s="1" t="inlineStr"/>
-      <c r="N22" s="1" t="inlineStr"/>
-      <c r="O22" s="1" t="inlineStr"/>
-      <c r="P22" s="1" t="inlineStr"/>
-      <c r="Q22" s="1" t="inlineStr"/>
-      <c r="R22" s="1" t="inlineStr"/>
-      <c r="S22" s="1" t="inlineStr"/>
-      <c r="T22" s="1" t="inlineStr"/>
-      <c r="U22" s="1" t="inlineStr"/>
-      <c r="V22" s="1" t="inlineStr"/>
-      <c r="W22" s="1" t="inlineStr"/>
-      <c r="X22" s="1" t="inlineStr"/>
-      <c r="Y22" s="1" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr"/>
-      <c r="B23" s="1" t="inlineStr"/>
-      <c r="C23" s="1" t="inlineStr"/>
-      <c r="D23" s="1" t="inlineStr"/>
-      <c r="E23" s="1" t="inlineStr"/>
-      <c r="F23" s="1" t="inlineStr"/>
-      <c r="G23" s="1" t="inlineStr"/>
-      <c r="H23" s="1" t="inlineStr"/>
-      <c r="I23" s="1" t="inlineStr"/>
-      <c r="J23" s="1" t="inlineStr"/>
-      <c r="K23" s="1" t="inlineStr">
-        <is>
-          <t>L637: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: At Thursdayâ€™s session of the Council,</t>
-        </is>
-      </c>
-      <c r="L23" s="1" t="inlineStr"/>
-      <c r="M23" s="1" t="inlineStr"/>
-      <c r="N23" s="1" t="inlineStr"/>
-      <c r="O23" s="1" t="inlineStr"/>
-      <c r="P23" s="1" t="inlineStr"/>
-      <c r="Q23" s="1" t="inlineStr"/>
-      <c r="R23" s="1" t="inlineStr"/>
-      <c r="S23" s="1" t="inlineStr"/>
-      <c r="T23" s="1" t="inlineStr"/>
-      <c r="U23" s="1" t="inlineStr"/>
-      <c r="V23" s="1" t="inlineStr"/>
-      <c r="W23" s="1" t="inlineStr"/>
-      <c r="X23" s="1" t="inlineStr"/>
-      <c r="Y23" s="1" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr"/>
-      <c r="B24" s="1" t="inlineStr"/>
-      <c r="C24" s="1" t="inlineStr"/>
-      <c r="D24" s="1" t="inlineStr"/>
-      <c r="E24" s="1" t="inlineStr"/>
-      <c r="F24" s="1" t="inlineStr"/>
-      <c r="G24" s="1" t="inlineStr"/>
-      <c r="H24" s="1" t="inlineStr"/>
-      <c r="I24" s="1" t="inlineStr"/>
-      <c r="J24" s="1" t="inlineStr"/>
-      <c r="K24" s="1" t="inlineStr">
-        <is>
-          <t>L681: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: subject of the Churchâ€™s duty with reference</t>
-        </is>
-      </c>
-      <c r="L24" s="1" t="inlineStr"/>
-      <c r="M24" s="1" t="inlineStr"/>
-      <c r="N24" s="1" t="inlineStr"/>
-      <c r="O24" s="1" t="inlineStr"/>
-      <c r="P24" s="1" t="inlineStr"/>
-      <c r="Q24" s="1" t="inlineStr"/>
-      <c r="R24" s="1" t="inlineStr"/>
-      <c r="S24" s="1" t="inlineStr"/>
-      <c r="T24" s="1" t="inlineStr"/>
-      <c r="U24" s="1" t="inlineStr"/>
-      <c r="V24" s="1" t="inlineStr"/>
-      <c r="W24" s="1" t="inlineStr"/>
-      <c r="X24" s="1" t="inlineStr"/>
-      <c r="Y24" s="1" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr"/>
-      <c r="B25" s="1" t="inlineStr"/>
-      <c r="C25" s="1" t="inlineStr"/>
-      <c r="D25" s="1" t="inlineStr"/>
-      <c r="E25" s="1" t="inlineStr"/>
-      <c r="F25" s="1" t="inlineStr"/>
-      <c r="G25" s="1" t="inlineStr"/>
-      <c r="H25" s="1" t="inlineStr"/>
-      <c r="I25" s="1" t="inlineStr"/>
-      <c r="J25" s="1" t="inlineStr"/>
-      <c r="K25" s="1" t="inlineStr">
-        <is>
-          <t>L699: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: and eternal affairs last in menâ€™s thoughts.</t>
-        </is>
-      </c>
-      <c r="L25" s="1" t="inlineStr"/>
-      <c r="M25" s="1" t="inlineStr"/>
-      <c r="N25" s="1" t="inlineStr"/>
-      <c r="O25" s="1" t="inlineStr"/>
-      <c r="P25" s="1" t="inlineStr"/>
-      <c r="Q25" s="1" t="inlineStr"/>
-      <c r="R25" s="1" t="inlineStr"/>
-      <c r="S25" s="1" t="inlineStr"/>
-      <c r="T25" s="1" t="inlineStr"/>
-      <c r="U25" s="1" t="inlineStr"/>
-      <c r="V25" s="1" t="inlineStr"/>
-      <c r="W25" s="1" t="inlineStr"/>
-      <c r="X25" s="1" t="inlineStr"/>
-      <c r="Y25" s="1" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr"/>
-      <c r="B26" s="1" t="inlineStr"/>
-      <c r="C26" s="1" t="inlineStr"/>
-      <c r="D26" s="1" t="inlineStr"/>
-      <c r="E26" s="1" t="inlineStr"/>
-      <c r="F26" s="1" t="inlineStr"/>
-      <c r="G26" s="1" t="inlineStr"/>
-      <c r="H26" s="1" t="inlineStr"/>
-      <c r="I26" s="1" t="inlineStr"/>
-      <c r="J26" s="1" t="inlineStr"/>
-      <c r="K26" s="1" t="inlineStr">
-        <is>
-          <t>L709: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Church doing Godâ€™s will. Its opponents</t>
-        </is>
-      </c>
-      <c r="L26" s="1" t="inlineStr"/>
-      <c r="M26" s="1" t="inlineStr"/>
-      <c r="N26" s="1" t="inlineStr"/>
-      <c r="O26" s="1" t="inlineStr"/>
-      <c r="P26" s="1" t="inlineStr"/>
-      <c r="Q26" s="1" t="inlineStr"/>
-      <c r="R26" s="1" t="inlineStr"/>
-      <c r="S26" s="1" t="inlineStr"/>
-      <c r="T26" s="1" t="inlineStr"/>
-      <c r="U26" s="1" t="inlineStr"/>
-      <c r="V26" s="1" t="inlineStr"/>
-      <c r="W26" s="1" t="inlineStr"/>
-      <c r="X26" s="1" t="inlineStr"/>
-      <c r="Y26" s="1" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr"/>
-      <c r="B27" s="1" t="inlineStr"/>
-      <c r="C27" s="1" t="inlineStr"/>
-      <c r="D27" s="1" t="inlineStr"/>
-      <c r="E27" s="1" t="inlineStr"/>
-      <c r="F27" s="1" t="inlineStr"/>
-      <c r="G27" s="1" t="inlineStr"/>
-      <c r="H27" s="1" t="inlineStr"/>
-      <c r="I27" s="1" t="inlineStr"/>
-      <c r="J27" s="1" t="inlineStr"/>
-      <c r="K27" s="1" t="inlineStr">
-        <is>
-          <t>L727: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: OTTAWA, July 4.â€”Mr. Stewart, of Ottawa,</t>
-        </is>
-      </c>
-      <c r="L27" s="1" t="inlineStr"/>
-      <c r="M27" s="1" t="inlineStr"/>
-      <c r="N27" s="1" t="inlineStr"/>
-      <c r="O27" s="1" t="inlineStr"/>
-      <c r="P27" s="1" t="inlineStr"/>
-      <c r="Q27" s="1" t="inlineStr"/>
-      <c r="R27" s="1" t="inlineStr"/>
-      <c r="S27" s="1" t="inlineStr"/>
-      <c r="T27" s="1" t="inlineStr"/>
-      <c r="U27" s="1" t="inlineStr"/>
-      <c r="V27" s="1" t="inlineStr"/>
-      <c r="W27" s="1" t="inlineStr"/>
-      <c r="X27" s="1" t="inlineStr"/>
-      <c r="Y27" s="1" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr"/>
-      <c r="B28" s="1" t="inlineStr"/>
-      <c r="C28" s="1" t="inlineStr"/>
-      <c r="D28" s="1" t="inlineStr"/>
-      <c r="E28" s="1" t="inlineStr"/>
-      <c r="F28" s="1" t="inlineStr"/>
-      <c r="G28" s="1" t="inlineStr"/>
-      <c r="H28" s="1" t="inlineStr"/>
-      <c r="I28" s="1" t="inlineStr"/>
-      <c r="J28" s="1" t="inlineStr"/>
-      <c r="K28" s="1" t="inlineStr">
-        <is>
-          <t>L742: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: WINNIPEG, July 5.â€”For some time past</t>
-        </is>
-      </c>
-      <c r="L28" s="1" t="inlineStr"/>
-      <c r="M28" s="1" t="inlineStr"/>
-      <c r="N28" s="1" t="inlineStr"/>
-      <c r="O28" s="1" t="inlineStr"/>
-      <c r="P28" s="1" t="inlineStr"/>
-      <c r="Q28" s="1" t="inlineStr"/>
-      <c r="R28" s="1" t="inlineStr"/>
-      <c r="S28" s="1" t="inlineStr"/>
-      <c r="T28" s="1" t="inlineStr"/>
-      <c r="U28" s="1" t="inlineStr"/>
-      <c r="V28" s="1" t="inlineStr"/>
-      <c r="W28" s="1" t="inlineStr"/>
-      <c r="X28" s="1" t="inlineStr"/>
-      <c r="Y28" s="1" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr"/>
-      <c r="B29" s="1" t="inlineStr"/>
-      <c r="C29" s="1" t="inlineStr"/>
-      <c r="D29" s="1" t="inlineStr"/>
-      <c r="E29" s="1" t="inlineStr"/>
-      <c r="F29" s="1" t="inlineStr"/>
-      <c r="G29" s="1" t="inlineStr"/>
-      <c r="H29" s="1" t="inlineStr"/>
-      <c r="I29" s="1" t="inlineStr"/>
-      <c r="J29" s="1" t="inlineStr"/>
-      <c r="K29" s="1" t="inlineStr">
-        <is>
-          <t>L766: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Oâ€™Brien, resides at Killarney, and formerly</t>
-        </is>
-      </c>
-      <c r="L29" s="1" t="inlineStr"/>
-      <c r="M29" s="1" t="inlineStr"/>
-      <c r="N29" s="1" t="inlineStr"/>
-      <c r="O29" s="1" t="inlineStr"/>
-      <c r="P29" s="1" t="inlineStr"/>
-      <c r="Q29" s="1" t="inlineStr"/>
-      <c r="R29" s="1" t="inlineStr"/>
-      <c r="S29" s="1" t="inlineStr"/>
-      <c r="T29" s="1" t="inlineStr"/>
-      <c r="U29" s="1" t="inlineStr"/>
-      <c r="V29" s="1" t="inlineStr"/>
-      <c r="W29" s="1" t="inlineStr"/>
-      <c r="X29" s="1" t="inlineStr"/>
-      <c r="Y29" s="1" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr"/>
-      <c r="B30" s="1" t="inlineStr"/>
-      <c r="C30" s="1" t="inlineStr"/>
-      <c r="D30" s="1" t="inlineStr"/>
-      <c r="E30" s="1" t="inlineStr"/>
-      <c r="F30" s="1" t="inlineStr"/>
-      <c r="G30" s="1" t="inlineStr"/>
-      <c r="H30" s="1" t="inlineStr"/>
-      <c r="I30" s="1" t="inlineStr"/>
-      <c r="J30" s="1" t="inlineStr"/>
-      <c r="K30" s="1" t="inlineStr">
-        <is>
-          <t>L770: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: badly beaten the boy Oâ€™Brien and others.</t>
-        </is>
-      </c>
-      <c r="L30" s="1" t="inlineStr"/>
-      <c r="M30" s="1" t="inlineStr"/>
-      <c r="N30" s="1" t="inlineStr"/>
-      <c r="O30" s="1" t="inlineStr"/>
-      <c r="P30" s="1" t="inlineStr"/>
-      <c r="Q30" s="1" t="inlineStr"/>
-      <c r="R30" s="1" t="inlineStr"/>
-      <c r="S30" s="1" t="inlineStr"/>
-      <c r="T30" s="1" t="inlineStr"/>
-      <c r="U30" s="1" t="inlineStr"/>
-      <c r="V30" s="1" t="inlineStr"/>
-      <c r="W30" s="1" t="inlineStr"/>
-      <c r="X30" s="1" t="inlineStr"/>
-      <c r="Y30" s="1" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr"/>
-      <c r="B31" s="1" t="inlineStr"/>
-      <c r="C31" s="1" t="inlineStr"/>
-      <c r="D31" s="1" t="inlineStr"/>
-      <c r="E31" s="1" t="inlineStr"/>
-      <c r="F31" s="1" t="inlineStr"/>
-      <c r="G31" s="1" t="inlineStr"/>
-      <c r="H31" s="1" t="inlineStr"/>
-      <c r="I31" s="1" t="inlineStr"/>
-      <c r="J31" s="1" t="inlineStr"/>
-      <c r="K31" s="1" t="inlineStr">
-        <is>
-          <t>L773: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: oâ€™clock that night. He claims to have had</t>
-        </is>
-      </c>
-      <c r="L31" s="1" t="inlineStr"/>
-      <c r="M31" s="1" t="inlineStr"/>
-      <c r="N31" s="1" t="inlineStr"/>
-      <c r="O31" s="1" t="inlineStr"/>
-      <c r="P31" s="1" t="inlineStr"/>
-      <c r="Q31" s="1" t="inlineStr"/>
-      <c r="R31" s="1" t="inlineStr"/>
-      <c r="S31" s="1" t="inlineStr"/>
-      <c r="T31" s="1" t="inlineStr"/>
-      <c r="U31" s="1" t="inlineStr"/>
-      <c r="V31" s="1" t="inlineStr"/>
-      <c r="W31" s="1" t="inlineStr"/>
-      <c r="X31" s="1" t="inlineStr"/>
-      <c r="Y31" s="1" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr"/>
-      <c r="B32" s="1" t="inlineStr"/>
-      <c r="C32" s="1" t="inlineStr"/>
-      <c r="D32" s="1" t="inlineStr"/>
-      <c r="E32" s="1" t="inlineStr"/>
-      <c r="F32" s="1" t="inlineStr"/>
-      <c r="G32" s="1" t="inlineStr"/>
-      <c r="H32" s="1" t="inlineStr"/>
-      <c r="I32" s="1" t="inlineStr"/>
-      <c r="J32" s="1" t="inlineStr"/>
-      <c r="K32" s="1" t="inlineStr">
-        <is>
-          <t>L775: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: a gold piece in the saloon. It is said Oâ€™Brien</t>
-        </is>
-      </c>
-      <c r="L32" s="1" t="inlineStr"/>
-      <c r="M32" s="1" t="inlineStr"/>
-      <c r="N32" s="1" t="inlineStr"/>
-      <c r="O32" s="1" t="inlineStr"/>
-      <c r="P32" s="1" t="inlineStr"/>
-      <c r="Q32" s="1" t="inlineStr"/>
-      <c r="R32" s="1" t="inlineStr"/>
-      <c r="S32" s="1" t="inlineStr"/>
-      <c r="T32" s="1" t="inlineStr"/>
-      <c r="U32" s="1" t="inlineStr"/>
-      <c r="V32" s="1" t="inlineStr"/>
-      <c r="W32" s="1" t="inlineStr"/>
-      <c r="X32" s="1" t="inlineStr"/>
-      <c r="Y32" s="1" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr"/>
-      <c r="B33" s="1" t="inlineStr"/>
-      <c r="C33" s="1" t="inlineStr"/>
-      <c r="D33" s="1" t="inlineStr"/>
-      <c r="E33" s="1" t="inlineStr"/>
-      <c r="F33" s="1" t="inlineStr"/>
-      <c r="G33" s="1" t="inlineStr"/>
-      <c r="H33" s="1" t="inlineStr"/>
-      <c r="I33" s="1" t="inlineStr"/>
-      <c r="J33" s="1" t="inlineStr"/>
-      <c r="K33" s="1" t="inlineStr">
-        <is>
-          <t>L779: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: found by the doctor. Oâ€™Brien is not dead,</t>
-        </is>
-      </c>
-      <c r="L33" s="1" t="inlineStr"/>
-      <c r="M33" s="1" t="inlineStr"/>
-      <c r="N33" s="1" t="inlineStr"/>
-      <c r="O33" s="1" t="inlineStr"/>
-      <c r="P33" s="1" t="inlineStr"/>
-      <c r="Q33" s="1" t="inlineStr"/>
-      <c r="R33" s="1" t="inlineStr"/>
-      <c r="S33" s="1" t="inlineStr"/>
-      <c r="T33" s="1" t="inlineStr"/>
-      <c r="U33" s="1" t="inlineStr"/>
-      <c r="V33" s="1" t="inlineStr"/>
-      <c r="W33" s="1" t="inlineStr"/>
-      <c r="X33" s="1" t="inlineStr"/>
-      <c r="Y33" s="1" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr"/>
-      <c r="B34" s="1" t="inlineStr"/>
-      <c r="C34" s="1" t="inlineStr"/>
-      <c r="D34" s="1" t="inlineStr"/>
-      <c r="E34" s="1" t="inlineStr"/>
-      <c r="F34" s="1" t="inlineStr"/>
-      <c r="G34" s="1" t="inlineStr"/>
-      <c r="H34" s="1" t="inlineStr"/>
-      <c r="I34" s="1" t="inlineStr"/>
-      <c r="J34" s="1" t="inlineStr"/>
-      <c r="K34" s="1" t="inlineStr">
-        <is>
-          <t>L794: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: WINNIPEG, July 6.â€”The Provincial Sun-</t>
-        </is>
-      </c>
-      <c r="L34" s="1" t="inlineStr"/>
-      <c r="M34" s="1" t="inlineStr"/>
-      <c r="N34" s="1" t="inlineStr"/>
-      <c r="O34" s="1" t="inlineStr"/>
-      <c r="P34" s="1" t="inlineStr"/>
-      <c r="Q34" s="1" t="inlineStr"/>
-      <c r="R34" s="1" t="inlineStr"/>
-      <c r="S34" s="1" t="inlineStr"/>
-      <c r="T34" s="1" t="inlineStr"/>
-      <c r="U34" s="1" t="inlineStr"/>
-      <c r="V34" s="1" t="inlineStr"/>
-      <c r="W34" s="1" t="inlineStr"/>
-      <c r="X34" s="1" t="inlineStr"/>
-      <c r="Y34" s="1" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr"/>
-      <c r="B35" s="1" t="inlineStr"/>
-      <c r="C35" s="1" t="inlineStr"/>
-      <c r="D35" s="1" t="inlineStr"/>
-      <c r="E35" s="1" t="inlineStr"/>
-      <c r="F35" s="1" t="inlineStr"/>
-      <c r="G35" s="1" t="inlineStr"/>
-      <c r="H35" s="1" t="inlineStr"/>
-      <c r="I35" s="1" t="inlineStr"/>
-      <c r="J35" s="1" t="inlineStr"/>
-      <c r="K35" s="1" t="inlineStr">
-        <is>
-          <t>L814: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: end. Careyâ€™s grave adjoins that of a name-</t>
-        </is>
-      </c>
-      <c r="L35" s="1" t="inlineStr"/>
-      <c r="M35" s="1" t="inlineStr"/>
-      <c r="N35" s="1" t="inlineStr"/>
-      <c r="O35" s="1" t="inlineStr"/>
-      <c r="P35" s="1" t="inlineStr"/>
-      <c r="Q35" s="1" t="inlineStr"/>
-      <c r="R35" s="1" t="inlineStr"/>
-      <c r="S35" s="1" t="inlineStr"/>
-      <c r="T35" s="1" t="inlineStr"/>
-      <c r="U35" s="1" t="inlineStr"/>
-      <c r="V35" s="1" t="inlineStr"/>
-      <c r="W35" s="1" t="inlineStr"/>
-      <c r="X35" s="1" t="inlineStr"/>
-      <c r="Y35" s="1" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr"/>
-      <c r="B36" s="1" t="inlineStr"/>
-      <c r="C36" s="1" t="inlineStr"/>
-      <c r="D36" s="1" t="inlineStr"/>
-      <c r="E36" s="1" t="inlineStr"/>
-      <c r="F36" s="1" t="inlineStr"/>
-      <c r="G36" s="1" t="inlineStr"/>
-      <c r="H36" s="1" t="inlineStr"/>
-      <c r="I36" s="1" t="inlineStr"/>
-      <c r="J36" s="1" t="inlineStr"/>
-      <c r="K36" s="1" t="inlineStr">
-        <is>
-          <t>L841: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: LONDON, Ont., July 6.â€”A conference of</t>
-        </is>
-      </c>
-      <c r="L36" s="1" t="inlineStr"/>
-      <c r="M36" s="1" t="inlineStr"/>
-      <c r="N36" s="1" t="inlineStr"/>
-      <c r="O36" s="1" t="inlineStr"/>
-      <c r="P36" s="1" t="inlineStr"/>
-      <c r="Q36" s="1" t="inlineStr"/>
-      <c r="R36" s="1" t="inlineStr"/>
-      <c r="S36" s="1" t="inlineStr"/>
-      <c r="T36" s="1" t="inlineStr"/>
-      <c r="U36" s="1" t="inlineStr"/>
-      <c r="V36" s="1" t="inlineStr"/>
-      <c r="W36" s="1" t="inlineStr"/>
-      <c r="X36" s="1" t="inlineStr"/>
-      <c r="Y36" s="1" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr"/>
-      <c r="B37" s="1" t="inlineStr"/>
-      <c r="C37" s="1" t="inlineStr"/>
-      <c r="D37" s="1" t="inlineStr"/>
-      <c r="E37" s="1" t="inlineStr"/>
-      <c r="F37" s="1" t="inlineStr"/>
-      <c r="G37" s="1" t="inlineStr"/>
-      <c r="H37" s="1" t="inlineStr"/>
-      <c r="I37" s="1" t="inlineStr"/>
-      <c r="J37" s="1" t="inlineStr"/>
-      <c r="K37" s="1" t="inlineStr">
-        <is>
-          <t>L852: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: WINNIPEG, Man., July 4.â€”The nomina-</t>
-        </is>
-      </c>
-      <c r="L37" s="1" t="inlineStr"/>
-      <c r="M37" s="1" t="inlineStr"/>
-      <c r="N37" s="1" t="inlineStr"/>
-      <c r="O37" s="1" t="inlineStr"/>
-      <c r="P37" s="1" t="inlineStr"/>
-      <c r="Q37" s="1" t="inlineStr"/>
-      <c r="R37" s="1" t="inlineStr"/>
-      <c r="S37" s="1" t="inlineStr"/>
-      <c r="T37" s="1" t="inlineStr"/>
-      <c r="U37" s="1" t="inlineStr"/>
-      <c r="V37" s="1" t="inlineStr"/>
-      <c r="W37" s="1" t="inlineStr"/>
-      <c r="X37" s="1" t="inlineStr"/>
-      <c r="Y37" s="1" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr"/>
-      <c r="B38" s="1" t="inlineStr"/>
-      <c r="C38" s="1" t="inlineStr"/>
-      <c r="D38" s="1" t="inlineStr"/>
-      <c r="E38" s="1" t="inlineStr"/>
-      <c r="F38" s="1" t="inlineStr"/>
-      <c r="G38" s="1" t="inlineStr"/>
-      <c r="H38" s="1" t="inlineStr"/>
-      <c r="I38" s="1" t="inlineStr"/>
-      <c r="J38" s="1" t="inlineStr"/>
-      <c r="K38" s="1" t="inlineStr">
-        <is>
-          <t>L880: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: BRANTFORD, July 5.â€”The unveiling of</t>
-        </is>
-      </c>
-      <c r="L38" s="1" t="inlineStr"/>
-      <c r="M38" s="1" t="inlineStr"/>
-      <c r="N38" s="1" t="inlineStr"/>
-      <c r="O38" s="1" t="inlineStr"/>
-      <c r="P38" s="1" t="inlineStr"/>
-      <c r="Q38" s="1" t="inlineStr"/>
-      <c r="R38" s="1" t="inlineStr"/>
-      <c r="S38" s="1" t="inlineStr"/>
-      <c r="T38" s="1" t="inlineStr"/>
-      <c r="U38" s="1" t="inlineStr"/>
-      <c r="V38" s="1" t="inlineStr"/>
-      <c r="W38" s="1" t="inlineStr"/>
-      <c r="X38" s="1" t="inlineStr"/>
-      <c r="Y38" s="1" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr"/>
-      <c r="B39" s="1" t="inlineStr"/>
-      <c r="C39" s="1" t="inlineStr"/>
-      <c r="D39" s="1" t="inlineStr"/>
-      <c r="E39" s="1" t="inlineStr"/>
-      <c r="F39" s="1" t="inlineStr"/>
-      <c r="G39" s="1" t="inlineStr"/>
-      <c r="H39" s="1" t="inlineStr"/>
-      <c r="I39" s="1" t="inlineStr"/>
-      <c r="J39" s="1" t="inlineStr"/>
-      <c r="K39" s="1" t="inlineStr">
-        <is>
-          <t>L927: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: and his boat from the pool before passing | SWEABURG, July 4.â€”To day was a gala</t>
-        </is>
-      </c>
-      <c r="L39" s="1" t="inlineStr"/>
-      <c r="M39" s="1" t="inlineStr"/>
-      <c r="N39" s="1" t="inlineStr"/>
-      <c r="O39" s="1" t="inlineStr"/>
-      <c r="P39" s="1" t="inlineStr"/>
-      <c r="Q39" s="1" t="inlineStr"/>
-      <c r="R39" s="1" t="inlineStr"/>
-      <c r="S39" s="1" t="inlineStr"/>
-      <c r="T39" s="1" t="inlineStr"/>
-      <c r="U39" s="1" t="inlineStr"/>
-      <c r="V39" s="1" t="inlineStr"/>
-      <c r="W39" s="1" t="inlineStr"/>
-      <c r="X39" s="1" t="inlineStr"/>
-      <c r="Y39" s="1" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr"/>
-      <c r="B40" s="1" t="inlineStr"/>
-      <c r="C40" s="1" t="inlineStr"/>
-      <c r="D40" s="1" t="inlineStr"/>
-      <c r="E40" s="1" t="inlineStr"/>
-      <c r="F40" s="1" t="inlineStr"/>
-      <c r="G40" s="1" t="inlineStr"/>
-      <c r="H40" s="1" t="inlineStr"/>
-      <c r="I40" s="1" t="inlineStr"/>
-      <c r="J40" s="1" t="inlineStr"/>
-      <c r="K40" s="1" t="inlineStr">
-        <is>
-          <t>L929: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: rapids, he engaged â€˜a hack, drove over thethat Sir Richard Cartwright, representa-</t>
-        </is>
-      </c>
-      <c r="L40" s="1" t="inlineStr"/>
-      <c r="M40" s="1" t="inlineStr"/>
-      <c r="N40" s="1" t="inlineStr"/>
-      <c r="O40" s="1" t="inlineStr"/>
-      <c r="P40" s="1" t="inlineStr"/>
-      <c r="Q40" s="1" t="inlineStr"/>
-      <c r="R40" s="1" t="inlineStr"/>
-      <c r="S40" s="1" t="inlineStr"/>
-      <c r="T40" s="1" t="inlineStr"/>
-      <c r="U40" s="1" t="inlineStr"/>
-      <c r="V40" s="1" t="inlineStr"/>
-      <c r="W40" s="1" t="inlineStr"/>
-      <c r="X40" s="1" t="inlineStr"/>
-      <c r="Y40" s="1" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr"/>
-      <c r="B41" s="1" t="inlineStr"/>
-      <c r="C41" s="1" t="inlineStr"/>
-      <c r="D41" s="1" t="inlineStr"/>
-      <c r="E41" s="1" t="inlineStr"/>
-      <c r="F41" s="1" t="inlineStr"/>
-      <c r="G41" s="1" t="inlineStr"/>
-      <c r="H41" s="1" t="inlineStr"/>
-      <c r="I41" s="1" t="inlineStr"/>
-      <c r="J41" s="1" t="inlineStr"/>
-      <c r="K41" s="1" t="inlineStr">
-        <is>
-          <t>L945: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | line starts with digit/letter garbage token | suspicious token(s): 1self (letter/digit mix) :: 1self from the fastenings and failed. His | cost $6,000. At 3 oâ€™clock Mr. P. J. Cook,</t>
-        </is>
-      </c>
-      <c r="L41" s="1" t="inlineStr"/>
-      <c r="M41" s="1" t="inlineStr"/>
-      <c r="N41" s="1" t="inlineStr"/>
-      <c r="O41" s="1" t="inlineStr"/>
-      <c r="P41" s="1" t="inlineStr"/>
-      <c r="Q41" s="1" t="inlineStr"/>
-      <c r="R41" s="1" t="inlineStr"/>
-      <c r="S41" s="1" t="inlineStr"/>
-      <c r="T41" s="1" t="inlineStr"/>
-      <c r="U41" s="1" t="inlineStr"/>
-      <c r="V41" s="1" t="inlineStr"/>
-      <c r="W41" s="1" t="inlineStr"/>
-      <c r="X41" s="1" t="inlineStr"/>
-      <c r="Y41" s="1" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr"/>
-      <c r="B42" s="1" t="inlineStr"/>
-      <c r="C42" s="1" t="inlineStr"/>
-      <c r="D42" s="1" t="inlineStr"/>
-      <c r="E42" s="1" t="inlineStr"/>
-      <c r="F42" s="1" t="inlineStr"/>
-      <c r="G42" s="1" t="inlineStr"/>
-      <c r="H42" s="1" t="inlineStr"/>
-      <c r="I42" s="1" t="inlineStr"/>
-      <c r="J42" s="1" t="inlineStr"/>
-      <c r="K42" s="1" t="inlineStr">
-        <is>
-          <t>L950: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”his friends to take it across to the Ameri- proceeded in conformity with the form of</t>
-        </is>
-      </c>
-      <c r="L42" s="1" t="inlineStr"/>
-      <c r="M42" s="1" t="inlineStr"/>
-      <c r="N42" s="1" t="inlineStr"/>
-      <c r="O42" s="1" t="inlineStr"/>
-      <c r="P42" s="1" t="inlineStr"/>
-      <c r="Q42" s="1" t="inlineStr"/>
-      <c r="R42" s="1" t="inlineStr"/>
-      <c r="S42" s="1" t="inlineStr"/>
-      <c r="T42" s="1" t="inlineStr"/>
-      <c r="U42" s="1" t="inlineStr"/>
-      <c r="V42" s="1" t="inlineStr"/>
-      <c r="W42" s="1" t="inlineStr"/>
-      <c r="X42" s="1" t="inlineStr"/>
-      <c r="Y42" s="1" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="inlineStr"/>
-      <c r="B43" s="1" t="inlineStr"/>
-      <c r="C43" s="1" t="inlineStr"/>
-      <c r="D43" s="1" t="inlineStr"/>
-      <c r="E43" s="1" t="inlineStr"/>
-      <c r="F43" s="1" t="inlineStr"/>
-      <c r="G43" s="1" t="inlineStr"/>
-      <c r="H43" s="1" t="inlineStr"/>
-      <c r="I43" s="1" t="inlineStr"/>
-      <c r="J43" s="1" t="inlineStr"/>
-      <c r="K43" s="1" t="inlineStr">
-        <is>
-          <t>L951: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: -â€”can side of the river. There was no mark of | the Methodist discipline, well and truly to</t>
-        </is>
-      </c>
-      <c r="L43" s="1" t="inlineStr"/>
-      <c r="M43" s="1" t="inlineStr"/>
-      <c r="N43" s="1" t="inlineStr"/>
-      <c r="O43" s="1" t="inlineStr"/>
-      <c r="P43" s="1" t="inlineStr"/>
-      <c r="Q43" s="1" t="inlineStr"/>
-      <c r="R43" s="1" t="inlineStr"/>
-      <c r="S43" s="1" t="inlineStr"/>
-      <c r="T43" s="1" t="inlineStr"/>
-      <c r="U43" s="1" t="inlineStr"/>
-      <c r="V43" s="1" t="inlineStr"/>
-      <c r="W43" s="1" t="inlineStr"/>
-      <c r="X43" s="1" t="inlineStr"/>
-      <c r="Y43" s="1" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr"/>
-      <c r="B44" s="1" t="inlineStr"/>
-      <c r="C44" s="1" t="inlineStr"/>
-      <c r="D44" s="1" t="inlineStr"/>
-      <c r="E44" s="1" t="inlineStr"/>
-      <c r="F44" s="1" t="inlineStr"/>
-      <c r="G44" s="1" t="inlineStr"/>
-      <c r="H44" s="1" t="inlineStr"/>
-      <c r="I44" s="1" t="inlineStr"/>
-      <c r="J44" s="1" t="inlineStr"/>
-      <c r="K44" s="1" t="inlineStr">
-        <is>
-          <t>L964: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: To-dayâ€™s tragic affair only adds another | Sir Richard delivered a masterly address</t>
-        </is>
-      </c>
-      <c r="L44" s="1" t="inlineStr"/>
-      <c r="M44" s="1" t="inlineStr"/>
-      <c r="N44" s="1" t="inlineStr"/>
-      <c r="O44" s="1" t="inlineStr"/>
-      <c r="P44" s="1" t="inlineStr"/>
-      <c r="Q44" s="1" t="inlineStr"/>
-      <c r="R44" s="1" t="inlineStr"/>
-      <c r="S44" s="1" t="inlineStr"/>
-      <c r="T44" s="1" t="inlineStr"/>
-      <c r="U44" s="1" t="inlineStr"/>
-      <c r="V44" s="1" t="inlineStr"/>
-      <c r="W44" s="1" t="inlineStr"/>
-      <c r="X44" s="1" t="inlineStr"/>
-      <c r="Y44" s="1" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr"/>
-      <c r="B45" s="1" t="inlineStr"/>
-      <c r="C45" s="1" t="inlineStr"/>
-      <c r="D45" s="1" t="inlineStr"/>
-      <c r="E45" s="1" t="inlineStr"/>
-      <c r="F45" s="1" t="inlineStr"/>
-      <c r="G45" s="1" t="inlineStr"/>
-      <c r="H45" s="1" t="inlineStr"/>
-      <c r="I45" s="1" t="inlineStr"/>
-      <c r="J45" s="1" t="inlineStr"/>
-      <c r="K45" s="1" t="inlineStr">
-        <is>
-          <t>L980: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: ing the suit brought by Oâ€™Donnell amount</t>
-        </is>
-      </c>
-      <c r="L45" s="1" t="inlineStr"/>
-      <c r="M45" s="1" t="inlineStr"/>
-      <c r="N45" s="1" t="inlineStr"/>
-      <c r="O45" s="1" t="inlineStr"/>
-      <c r="P45" s="1" t="inlineStr"/>
-      <c r="Q45" s="1" t="inlineStr"/>
-      <c r="R45" s="1" t="inlineStr"/>
-      <c r="S45" s="1" t="inlineStr"/>
-      <c r="T45" s="1" t="inlineStr"/>
-      <c r="U45" s="1" t="inlineStr"/>
-      <c r="V45" s="1" t="inlineStr"/>
-      <c r="W45" s="1" t="inlineStr"/>
-      <c r="X45" s="1" t="inlineStr"/>
-      <c r="Y45" s="1" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="inlineStr"/>
-      <c r="B46" s="1" t="inlineStr"/>
-      <c r="C46" s="1" t="inlineStr"/>
-      <c r="D46" s="1" t="inlineStr"/>
-      <c r="E46" s="1" t="inlineStr"/>
-      <c r="F46" s="1" t="inlineStr"/>
-      <c r="G46" s="1" t="inlineStr"/>
-      <c r="H46" s="1" t="inlineStr"/>
-      <c r="I46" s="1" t="inlineStr"/>
-      <c r="J46" s="1" t="inlineStr"/>
-      <c r="K46" s="1" t="inlineStr">
-        <is>
-          <t>L982: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Oâ€™Donnell liable for the amount.</t>
-        </is>
-      </c>
-      <c r="L46" s="1" t="inlineStr"/>
-      <c r="M46" s="1" t="inlineStr"/>
-      <c r="N46" s="1" t="inlineStr"/>
-      <c r="O46" s="1" t="inlineStr"/>
-      <c r="P46" s="1" t="inlineStr"/>
-      <c r="Q46" s="1" t="inlineStr"/>
-      <c r="R46" s="1" t="inlineStr"/>
-      <c r="S46" s="1" t="inlineStr"/>
-      <c r="T46" s="1" t="inlineStr"/>
-      <c r="U46" s="1" t="inlineStr"/>
-      <c r="V46" s="1" t="inlineStr"/>
-      <c r="W46" s="1" t="inlineStr"/>
-      <c r="X46" s="1" t="inlineStr"/>
-      <c r="Y46" s="1" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="inlineStr"/>
-      <c r="B47" s="1" t="inlineStr"/>
-      <c r="C47" s="1" t="inlineStr"/>
-      <c r="D47" s="1" t="inlineStr"/>
-      <c r="E47" s="1" t="inlineStr"/>
-      <c r="F47" s="1" t="inlineStr"/>
-      <c r="G47" s="1" t="inlineStr"/>
-      <c r="H47" s="1" t="inlineStr"/>
-      <c r="I47" s="1" t="inlineStr"/>
-      <c r="J47" s="1" t="inlineStr"/>
-      <c r="K47" s="1" t="inlineStr">
-        <is>
-          <t>L1025: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: LONDON, July 4.â€”Rev. Father Pender-</t>
-        </is>
-      </c>
-      <c r="L47" s="1" t="inlineStr"/>
-      <c r="M47" s="1" t="inlineStr"/>
-      <c r="N47" s="1" t="inlineStr"/>
-      <c r="O47" s="1" t="inlineStr"/>
-      <c r="P47" s="1" t="inlineStr"/>
-      <c r="Q47" s="1" t="inlineStr"/>
-      <c r="R47" s="1" t="inlineStr"/>
-      <c r="S47" s="1" t="inlineStr"/>
-      <c r="T47" s="1" t="inlineStr"/>
-      <c r="U47" s="1" t="inlineStr"/>
-      <c r="V47" s="1" t="inlineStr"/>
-      <c r="W47" s="1" t="inlineStr"/>
-      <c r="X47" s="1" t="inlineStr"/>
-      <c r="Y47" s="1" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr"/>
-      <c r="B48" s="1" t="inlineStr"/>
-      <c r="C48" s="1" t="inlineStr"/>
-      <c r="D48" s="1" t="inlineStr"/>
-      <c r="E48" s="1" t="inlineStr"/>
-      <c r="F48" s="1" t="inlineStr"/>
-      <c r="G48" s="1" t="inlineStr"/>
-      <c r="H48" s="1" t="inlineStr"/>
-      <c r="I48" s="1" t="inlineStr"/>
-      <c r="J48" s="1" t="inlineStr"/>
-      <c r="K48" s="1" t="inlineStr">
-        <is>
-          <t>L1032: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: he went to St. Josephâ€™s Convent, Somerset,</t>
-        </is>
-      </c>
-      <c r="L48" s="1" t="inlineStr"/>
-      <c r="M48" s="1" t="inlineStr"/>
-      <c r="N48" s="1" t="inlineStr"/>
-      <c r="O48" s="1" t="inlineStr"/>
-      <c r="P48" s="1" t="inlineStr"/>
-      <c r="Q48" s="1" t="inlineStr"/>
-      <c r="R48" s="1" t="inlineStr"/>
-      <c r="S48" s="1" t="inlineStr"/>
-      <c r="T48" s="1" t="inlineStr"/>
-      <c r="U48" s="1" t="inlineStr"/>
-      <c r="V48" s="1" t="inlineStr"/>
-      <c r="W48" s="1" t="inlineStr"/>
-      <c r="X48" s="1" t="inlineStr"/>
-      <c r="Y48" s="1" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="inlineStr"/>
-      <c r="B49" s="1" t="inlineStr"/>
-      <c r="C49" s="1" t="inlineStr"/>
-      <c r="D49" s="1" t="inlineStr"/>
-      <c r="E49" s="1" t="inlineStr"/>
-      <c r="F49" s="1" t="inlineStr"/>
-      <c r="G49" s="1" t="inlineStr"/>
-      <c r="H49" s="1" t="inlineStr"/>
-      <c r="I49" s="1" t="inlineStr"/>
-      <c r="J49" s="1" t="inlineStr"/>
-      <c r="K49" s="1" t="inlineStr">
-        <is>
-          <t>L1042: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Horsfordâ€™s Acid Phosphate</t>
-        </is>
-      </c>
-      <c r="L49" s="1" t="inlineStr"/>
-      <c r="M49" s="1" t="inlineStr"/>
-      <c r="N49" s="1" t="inlineStr"/>
-      <c r="O49" s="1" t="inlineStr"/>
-      <c r="P49" s="1" t="inlineStr"/>
-      <c r="Q49" s="1" t="inlineStr"/>
-      <c r="R49" s="1" t="inlineStr"/>
-      <c r="S49" s="1" t="inlineStr"/>
-      <c r="T49" s="1" t="inlineStr"/>
-      <c r="U49" s="1" t="inlineStr"/>
-      <c r="V49" s="1" t="inlineStr"/>
-      <c r="W49" s="1" t="inlineStr"/>
-      <c r="X49" s="1" t="inlineStr"/>
-      <c r="Y49" s="1" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="inlineStr"/>
-      <c r="B50" s="1" t="inlineStr"/>
-      <c r="C50" s="1" t="inlineStr"/>
-      <c r="D50" s="1" t="inlineStr"/>
-      <c r="E50" s="1" t="inlineStr"/>
-      <c r="F50" s="1" t="inlineStr"/>
-      <c r="G50" s="1" t="inlineStr"/>
-      <c r="H50" s="1" t="inlineStr"/>
-      <c r="I50" s="1" t="inlineStr"/>
-      <c r="J50" s="1" t="inlineStr"/>
-      <c r="K50" s="1" t="inlineStr">
-        <is>
-          <t>L1051: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: of the digestive organs.â€�</t>
-        </is>
-      </c>
-      <c r="L50" s="1" t="inlineStr"/>
-      <c r="M50" s="1" t="inlineStr"/>
-      <c r="N50" s="1" t="inlineStr"/>
-      <c r="O50" s="1" t="inlineStr"/>
-      <c r="P50" s="1" t="inlineStr"/>
-      <c r="Q50" s="1" t="inlineStr"/>
-      <c r="R50" s="1" t="inlineStr"/>
-      <c r="S50" s="1" t="inlineStr"/>
-      <c r="T50" s="1" t="inlineStr"/>
-      <c r="U50" s="1" t="inlineStr"/>
-      <c r="V50" s="1" t="inlineStr"/>
-      <c r="W50" s="1" t="inlineStr"/>
-      <c r="X50" s="1" t="inlineStr"/>
-      <c r="Y50" s="1" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr"/>
-      <c r="B51" s="1" t="inlineStr"/>
-      <c r="C51" s="1" t="inlineStr"/>
-      <c r="D51" s="1" t="inlineStr"/>
-      <c r="E51" s="1" t="inlineStr"/>
-      <c r="F51" s="1" t="inlineStr"/>
-      <c r="G51" s="1" t="inlineStr"/>
-      <c r="H51" s="1" t="inlineStr"/>
-      <c r="I51" s="1" t="inlineStr"/>
-      <c r="J51" s="1" t="inlineStr"/>
-      <c r="K51" s="1" t="inlineStr">
-        <is>
-          <t>L1063: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: seat on the judgesâ€™ stand, and while chat-</t>
-        </is>
-      </c>
-      <c r="L51" s="1" t="inlineStr"/>
-      <c r="M51" s="1" t="inlineStr"/>
-      <c r="N51" s="1" t="inlineStr"/>
-      <c r="O51" s="1" t="inlineStr"/>
-      <c r="P51" s="1" t="inlineStr"/>
-      <c r="Q51" s="1" t="inlineStr"/>
-      <c r="R51" s="1" t="inlineStr"/>
-      <c r="S51" s="1" t="inlineStr"/>
-      <c r="T51" s="1" t="inlineStr"/>
-      <c r="U51" s="1" t="inlineStr"/>
-      <c r="V51" s="1" t="inlineStr"/>
-      <c r="W51" s="1" t="inlineStr"/>
-      <c r="X51" s="1" t="inlineStr"/>
-      <c r="Y51" s="1" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="inlineStr"/>
-      <c r="B52" s="1" t="inlineStr"/>
-      <c r="C52" s="1" t="inlineStr"/>
-      <c r="D52" s="1" t="inlineStr"/>
-      <c r="E52" s="1" t="inlineStr"/>
-      <c r="F52" s="1" t="inlineStr"/>
-      <c r="G52" s="1" t="inlineStr"/>
-      <c r="H52" s="1" t="inlineStr"/>
-      <c r="I52" s="1" t="inlineStr"/>
-      <c r="J52" s="1" t="inlineStr"/>
-      <c r="K52" s="1" t="inlineStr">
-        <is>
-          <t>L1068: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: bruised.â€”Stratford Beacon.</t>
-        </is>
-      </c>
-      <c r="L52" s="1" t="inlineStr"/>
-      <c r="M52" s="1" t="inlineStr"/>
-      <c r="N52" s="1" t="inlineStr"/>
-      <c r="O52" s="1" t="inlineStr"/>
-      <c r="P52" s="1" t="inlineStr"/>
-      <c r="Q52" s="1" t="inlineStr"/>
-      <c r="R52" s="1" t="inlineStr"/>
-      <c r="S52" s="1" t="inlineStr"/>
-      <c r="T52" s="1" t="inlineStr"/>
-      <c r="U52" s="1" t="inlineStr"/>
-      <c r="V52" s="1" t="inlineStr"/>
-      <c r="W52" s="1" t="inlineStr"/>
-      <c r="X52" s="1" t="inlineStr"/>
-      <c r="Y52" s="1" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="1" t="inlineStr"/>
-      <c r="B53" s="1" t="inlineStr"/>
-      <c r="C53" s="1" t="inlineStr"/>
-      <c r="D53" s="1" t="inlineStr"/>
-      <c r="E53" s="1" t="inlineStr"/>
-      <c r="F53" s="1" t="inlineStr"/>
-      <c r="G53" s="1" t="inlineStr"/>
-      <c r="H53" s="1" t="inlineStr"/>
-      <c r="I53" s="1" t="inlineStr"/>
-      <c r="J53" s="1" t="inlineStr"/>
-      <c r="K53" s="1" t="inlineStr">
-        <is>
-          <t>L1070: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: A Jockeyâ€™s Fatal Experiment.</t>
-        </is>
-      </c>
-      <c r="L53" s="1" t="inlineStr"/>
-      <c r="M53" s="1" t="inlineStr"/>
-      <c r="N53" s="1" t="inlineStr"/>
-      <c r="O53" s="1" t="inlineStr"/>
-      <c r="P53" s="1" t="inlineStr"/>
-      <c r="Q53" s="1" t="inlineStr"/>
-      <c r="R53" s="1" t="inlineStr"/>
-      <c r="S53" s="1" t="inlineStr"/>
-      <c r="T53" s="1" t="inlineStr"/>
-      <c r="U53" s="1" t="inlineStr"/>
-      <c r="V53" s="1" t="inlineStr"/>
-      <c r="W53" s="1" t="inlineStr"/>
-      <c r="X53" s="1" t="inlineStr"/>
-      <c r="Y53" s="1" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="inlineStr"/>
-      <c r="B54" s="1" t="inlineStr"/>
-      <c r="C54" s="1" t="inlineStr"/>
-      <c r="D54" s="1" t="inlineStr"/>
-      <c r="E54" s="1" t="inlineStr"/>
-      <c r="F54" s="1" t="inlineStr"/>
-      <c r="G54" s="1" t="inlineStr"/>
-      <c r="H54" s="1" t="inlineStr"/>
-      <c r="I54" s="1" t="inlineStr"/>
-      <c r="J54" s="1" t="inlineStr"/>
-      <c r="K54" s="1" t="inlineStr">
-        <is>
-          <t>L1073: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Adams, an employee in Shawâ€™s livery</t>
-        </is>
-      </c>
-      <c r="L54" s="1" t="inlineStr"/>
-      <c r="M54" s="1" t="inlineStr"/>
-      <c r="N54" s="1" t="inlineStr"/>
-      <c r="O54" s="1" t="inlineStr"/>
-      <c r="P54" s="1" t="inlineStr"/>
-      <c r="Q54" s="1" t="inlineStr"/>
-      <c r="R54" s="1" t="inlineStr"/>
-      <c r="S54" s="1" t="inlineStr"/>
-      <c r="T54" s="1" t="inlineStr"/>
-      <c r="U54" s="1" t="inlineStr"/>
-      <c r="V54" s="1" t="inlineStr"/>
-      <c r="W54" s="1" t="inlineStr"/>
-      <c r="X54" s="1" t="inlineStr"/>
-      <c r="Y54" s="1" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="inlineStr"/>
-      <c r="B55" s="1" t="inlineStr"/>
-      <c r="C55" s="1" t="inlineStr"/>
-      <c r="D55" s="1" t="inlineStr"/>
-      <c r="E55" s="1" t="inlineStr"/>
-      <c r="F55" s="1" t="inlineStr"/>
-      <c r="G55" s="1" t="inlineStr"/>
-      <c r="H55" s="1" t="inlineStr"/>
-      <c r="I55" s="1" t="inlineStr"/>
-      <c r="J55" s="1" t="inlineStr"/>
-      <c r="K55" s="1" t="inlineStr">
-        <is>
-          <t>L1087: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: PAISLEY, July 4.â€”About 10.30 this morn-</t>
-        </is>
-      </c>
-      <c r="L55" s="1" t="inlineStr"/>
-      <c r="M55" s="1" t="inlineStr"/>
-      <c r="N55" s="1" t="inlineStr"/>
-      <c r="O55" s="1" t="inlineStr"/>
-      <c r="P55" s="1" t="inlineStr"/>
-      <c r="Q55" s="1" t="inlineStr"/>
-      <c r="R55" s="1" t="inlineStr"/>
-      <c r="S55" s="1" t="inlineStr"/>
-      <c r="T55" s="1" t="inlineStr"/>
-      <c r="U55" s="1" t="inlineStr"/>
-      <c r="V55" s="1" t="inlineStr"/>
-      <c r="W55" s="1" t="inlineStr"/>
-      <c r="X55" s="1" t="inlineStr"/>
-      <c r="Y55" s="1" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="1" t="inlineStr"/>
-      <c r="B56" s="1" t="inlineStr"/>
-      <c r="C56" s="1" t="inlineStr"/>
-      <c r="D56" s="1" t="inlineStr"/>
-      <c r="E56" s="1" t="inlineStr"/>
-      <c r="F56" s="1" t="inlineStr"/>
-      <c r="G56" s="1" t="inlineStr"/>
-      <c r="H56" s="1" t="inlineStr"/>
-      <c r="I56" s="1" t="inlineStr"/>
-      <c r="J56" s="1" t="inlineStr"/>
-      <c r="K56" s="1" t="inlineStr">
-        <is>
-          <t>L1097: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Owing to the old gentlemanâ€™s courage the</t>
-        </is>
-      </c>
-      <c r="L56" s="1" t="inlineStr"/>
-      <c r="M56" s="1" t="inlineStr"/>
-      <c r="N56" s="1" t="inlineStr"/>
-      <c r="O56" s="1" t="inlineStr"/>
-      <c r="P56" s="1" t="inlineStr"/>
-      <c r="Q56" s="1" t="inlineStr"/>
-      <c r="R56" s="1" t="inlineStr"/>
-      <c r="S56" s="1" t="inlineStr"/>
-      <c r="T56" s="1" t="inlineStr"/>
-      <c r="U56" s="1" t="inlineStr"/>
-      <c r="V56" s="1" t="inlineStr"/>
-      <c r="W56" s="1" t="inlineStr"/>
-      <c r="X56" s="1" t="inlineStr"/>
-      <c r="Y56" s="1" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="1" t="inlineStr"/>
-      <c r="B57" s="1" t="inlineStr"/>
-      <c r="C57" s="1" t="inlineStr"/>
-      <c r="D57" s="1" t="inlineStr"/>
-      <c r="E57" s="1" t="inlineStr"/>
-      <c r="F57" s="1" t="inlineStr"/>
-      <c r="G57" s="1" t="inlineStr"/>
-      <c r="H57" s="1" t="inlineStr"/>
-      <c r="I57" s="1" t="inlineStr"/>
-      <c r="J57" s="1" t="inlineStr"/>
-      <c r="K57" s="1" t="inlineStr">
-        <is>
-          <t>L1100: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”Mr. Ira F. Calder has been appointed</t>
-        </is>
-      </c>
-      <c r="L57" s="1" t="inlineStr"/>
-      <c r="M57" s="1" t="inlineStr"/>
-      <c r="N57" s="1" t="inlineStr"/>
-      <c r="O57" s="1" t="inlineStr"/>
-      <c r="P57" s="1" t="inlineStr"/>
-      <c r="Q57" s="1" t="inlineStr"/>
-      <c r="R57" s="1" t="inlineStr"/>
-      <c r="S57" s="1" t="inlineStr"/>
-      <c r="T57" s="1" t="inlineStr"/>
-      <c r="U57" s="1" t="inlineStr"/>
-      <c r="V57" s="1" t="inlineStr"/>
-      <c r="W57" s="1" t="inlineStr"/>
-      <c r="X57" s="1" t="inlineStr"/>
-      <c r="Y57" s="1" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="1" t="inlineStr"/>
-      <c r="B58" s="1" t="inlineStr"/>
-      <c r="C58" s="1" t="inlineStr"/>
-      <c r="D58" s="1" t="inlineStr"/>
-      <c r="E58" s="1" t="inlineStr"/>
-      <c r="F58" s="1" t="inlineStr"/>
-      <c r="G58" s="1" t="inlineStr"/>
-      <c r="H58" s="1" t="inlineStr"/>
-      <c r="I58" s="1" t="inlineStr"/>
-      <c r="J58" s="1" t="inlineStr"/>
-      <c r="K58" s="1" t="inlineStr">
-        <is>
-          <t>L1105: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: laide street east, Toronto, while eating his â€”Bertie Galloway, daughter of Mr.</t>
-        </is>
-      </c>
-      <c r="L58" s="1" t="inlineStr"/>
-      <c r="M58" s="1" t="inlineStr"/>
-      <c r="N58" s="1" t="inlineStr"/>
-      <c r="O58" s="1" t="inlineStr"/>
-      <c r="P58" s="1" t="inlineStr"/>
-      <c r="Q58" s="1" t="inlineStr"/>
-      <c r="R58" s="1" t="inlineStr"/>
-      <c r="S58" s="1" t="inlineStr"/>
-      <c r="T58" s="1" t="inlineStr"/>
-      <c r="U58" s="1" t="inlineStr"/>
-      <c r="V58" s="1" t="inlineStr"/>
-      <c r="W58" s="1" t="inlineStr"/>
-      <c r="X58" s="1" t="inlineStr"/>
-      <c r="Y58" s="1" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="1" t="inlineStr"/>
-      <c r="B59" s="1" t="inlineStr"/>
-      <c r="C59" s="1" t="inlineStr"/>
-      <c r="D59" s="1" t="inlineStr"/>
-      <c r="E59" s="1" t="inlineStr"/>
-      <c r="F59" s="1" t="inlineStr"/>
-      <c r="G59" s="1" t="inlineStr"/>
-      <c r="H59" s="1" t="inlineStr"/>
-      <c r="I59" s="1" t="inlineStr"/>
-      <c r="J59" s="1" t="inlineStr"/>
-      <c r="K59" s="1" t="inlineStr">
-        <is>
-          <t>L1111: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: double/multiple hyphen :: stream, where Flack was continually -----------â€¢-------------</t>
-        </is>
-      </c>
-      <c r="L59" s="1" t="inlineStr"/>
-      <c r="M59" s="1" t="inlineStr"/>
-      <c r="N59" s="1" t="inlineStr"/>
-      <c r="O59" s="1" t="inlineStr"/>
-      <c r="P59" s="1" t="inlineStr"/>
-      <c r="Q59" s="1" t="inlineStr"/>
-      <c r="R59" s="1" t="inlineStr"/>
-      <c r="S59" s="1" t="inlineStr"/>
-      <c r="T59" s="1" t="inlineStr"/>
-      <c r="U59" s="1" t="inlineStr"/>
-      <c r="V59" s="1" t="inlineStr"/>
-      <c r="W59" s="1" t="inlineStr"/>
-      <c r="X59" s="1" t="inlineStr"/>
-      <c r="Y59" s="1" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="1" t="inlineStr"/>
-      <c r="B60" s="1" t="inlineStr"/>
-      <c r="C60" s="1" t="inlineStr"/>
-      <c r="D60" s="1" t="inlineStr"/>
-      <c r="E60" s="1" t="inlineStr"/>
-      <c r="F60" s="1" t="inlineStr"/>
-      <c r="G60" s="1" t="inlineStr"/>
-      <c r="H60" s="1" t="inlineStr"/>
-      <c r="I60" s="1" t="inlineStr"/>
-      <c r="J60" s="1" t="inlineStr"/>
-      <c r="K60" s="1" t="inlineStr">
-        <is>
-          <t>L1113: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ed by the breakers. â€”The project to supply St. Catharines</t>
-        </is>
-      </c>
-      <c r="L60" s="1" t="inlineStr"/>
-      <c r="M60" s="1" t="inlineStr"/>
-      <c r="N60" s="1" t="inlineStr"/>
-      <c r="O60" s="1" t="inlineStr"/>
-      <c r="P60" s="1" t="inlineStr"/>
-      <c r="Q60" s="1" t="inlineStr"/>
-      <c r="R60" s="1" t="inlineStr"/>
-      <c r="S60" s="1" t="inlineStr"/>
-      <c r="T60" s="1" t="inlineStr"/>
-      <c r="U60" s="1" t="inlineStr"/>
-      <c r="V60" s="1" t="inlineStr"/>
-      <c r="W60" s="1" t="inlineStr"/>
-      <c r="X60" s="1" t="inlineStr"/>
-      <c r="Y60" s="1" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
